--- a/Data Analysis/1_Data/Dominance_Experiment/dom_SOC_2017/bulk17_dom.xlsx
+++ b/Data Analysis/1_Data/Dominance_Experiment/dom_SOC_2017/bulk17_dom.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1437A674-E3FF-45BD-AB67-E2A983CE2BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E038994-4393-444B-BB0B-3F43C3AD56AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -561,7 +561,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.3016666666666667</v>
+        <v>1.3033333333333332</v>
       </c>
       <c r="C2"/>
     </row>
@@ -570,7 +570,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.3283333333333334</v>
+        <v>1.2875000000000001</v>
       </c>
       <c r="C3"/>
     </row>
@@ -579,7 +579,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.2933333333333332</v>
+        <v>1.3033333333333332</v>
       </c>
       <c r="C4"/>
     </row>
@@ -588,7 +588,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.3083333333333333</v>
+        <v>1.3166666666666667</v>
       </c>
       <c r="C5"/>
     </row>
@@ -597,7 +597,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.3133333333333332</v>
+        <v>1.2916666666666667</v>
       </c>
       <c r="C6"/>
     </row>
@@ -606,7 +606,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.2733333333333332</v>
+        <v>1.2891666666666666</v>
       </c>
       <c r="C7"/>
     </row>
@@ -615,7 +615,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.3733333333333333</v>
+        <v>1.2983333333333333</v>
       </c>
       <c r="C8"/>
     </row>
@@ -624,7 +624,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1.2850000000000001</v>
+        <v>1.2641666666666667</v>
       </c>
       <c r="C9"/>
     </row>
@@ -633,7 +633,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1.2566666666666666</v>
+        <v>1.2258333333333333</v>
       </c>
       <c r="C10"/>
     </row>
@@ -642,7 +642,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1.3166666666666667</v>
+        <v>1.2675000000000001</v>
       </c>
       <c r="C11"/>
     </row>
@@ -660,7 +660,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.2650000000000001</v>
+        <v>1.2975000000000001</v>
       </c>
       <c r="C13"/>
     </row>
@@ -669,7 +669,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.2750000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="C14"/>
     </row>
@@ -678,7 +678,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1.2416666666666669</v>
+        <v>1.2791666666666668</v>
       </c>
       <c r="C15"/>
     </row>
@@ -687,7 +687,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1.2716666666666667</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="C16"/>
     </row>
@@ -696,7 +696,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1.2283333333333333</v>
+        <v>1.2424999999999999</v>
       </c>
       <c r="C17"/>
     </row>
@@ -705,7 +705,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1.2416666666666667</v>
+        <v>1.2616666666666667</v>
       </c>
       <c r="C18"/>
     </row>
@@ -714,7 +714,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1.1983333333333333</v>
+        <v>1.2291666666666665</v>
       </c>
       <c r="C19"/>
     </row>
@@ -723,7 +723,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1.26</v>
+        <v>1.2633333333333332</v>
       </c>
       <c r="C20"/>
     </row>
@@ -732,7 +732,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1.2266666666666668</v>
+        <v>1.2308333333333334</v>
       </c>
       <c r="C21"/>
     </row>
@@ -741,7 +741,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>1.1983333333333333</v>
+        <v>1.2033333333333331</v>
       </c>
       <c r="C22"/>
     </row>
@@ -750,7 +750,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>1.165</v>
+        <v>1.1816666666666666</v>
       </c>
       <c r="C23"/>
     </row>
@@ -822,7 +822,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>1.343333333333333</v>
+        <v>1.3316666666666666</v>
       </c>
       <c r="C31"/>
     </row>
@@ -831,7 +831,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>1.2433333333333332</v>
+        <v>1.24</v>
       </c>
       <c r="C32"/>
     </row>
@@ -840,7 +840,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>1.2883333333333333</v>
+        <v>1.2841666666666667</v>
       </c>
       <c r="C33"/>
     </row>
@@ -849,7 +849,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>1.3099999999999998</v>
+        <v>1.3274999999999999</v>
       </c>
       <c r="C34"/>
     </row>
@@ -858,7 +858,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>1.3533333333333335</v>
+        <v>1.3716666666666666</v>
       </c>
       <c r="C35"/>
     </row>
@@ -867,7 +867,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>1.3399999999999999</v>
+        <v>1.3075000000000001</v>
       </c>
       <c r="C36"/>
     </row>
@@ -876,7 +876,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>1.3</v>
+        <v>1.2841666666666667</v>
       </c>
       <c r="C37"/>
     </row>
@@ -885,7 +885,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>1.2983333333333333</v>
+        <v>1.325</v>
       </c>
       <c r="C38"/>
     </row>
@@ -894,7 +894,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>1.3516666666666666</v>
+        <v>1.3325</v>
       </c>
       <c r="C39"/>
     </row>
